--- a/artfynd/A 1111-2024 artfynd.xlsx
+++ b/artfynd/A 1111-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1111-2024 artfynd.xlsx
+++ b/artfynd/A 1111-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66538160</v>
+        <v>66538149</v>
       </c>
       <c r="B2" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>366</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>378893.5320116376</v>
+        <v>378922</v>
       </c>
       <c r="R2" t="n">
-        <v>6614674.818325036</v>
+        <v>6614697</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,21 +743,11 @@
           <t>2012-05-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-05-18</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,7 +759,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>21004</t>
+          <t>20994</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,54 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66538171</v>
+        <v>66538160</v>
       </c>
       <c r="B3" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brunskogsfjället, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>378867.2177972872</v>
+        <v>378894</v>
       </c>
       <c r="R3" t="n">
-        <v>6614519.377899468</v>
+        <v>6614675</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -869,21 +845,11 @@
           <t>2012-05-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-05-18</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -895,7 +861,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>21014</t>
+          <t>21004</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -906,57 +872,56 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66538149</v>
+        <v>66538171</v>
       </c>
       <c r="B4" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brunskogsfjället, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>378922.1216419489</v>
+        <v>378867</v>
       </c>
       <c r="R4" t="n">
-        <v>6614697.158917764</v>
+        <v>6614519</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -986,21 +951,11 @@
           <t>2012-05-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-05-18</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1012,7 +967,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>20994</t>
+          <t>21014</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1023,7 +978,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1033,12 +988,7 @@
         <v>115478347</v>
       </c>
       <c r="B5" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,6 +1099,233 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>66538159</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Brunskogsfjället, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>378894</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6614675</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2012-05-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2012-05-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>spillning</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>21003</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>56039534</v>
+      </c>
+      <c r="B7" t="n">
+        <v>108774</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>231615</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rönnfibbla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hieracium cosmiodontum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Omang</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Brunskogsfjället, väst Nytorp, Vikene, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>378681</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6614571</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2015-06-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2015-06-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Beskuggad vägslänt</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>Anders Persson</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>PAP 122</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
